--- a/UV-Sheets_protocol.xlsx
+++ b/UV-Sheets_protocol.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,7 +497,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>alinden</t>
+          <t>troussea</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -530,7 +530,9 @@
       <c r="J2" t="n">
         <v>10</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -540,7 +542,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jmuelle4</t>
+          <t>troussea</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -571,7 +573,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fblessma</t>
+          <t>troussea</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -602,7 +604,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jmuelle4</t>
+          <t>troussea</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -633,7 +635,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>alinden</t>
+          <t>troussea</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -666,7 +668,9 @@
       <c r="J6" t="n">
         <v>5</v>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -676,7 +680,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jmuelle4</t>
+          <t>troussea</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -709,313 +713,9 @@
       <c r="J7" t="n">
         <v>6</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>UV-Sheet_0007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>UV-Sheet_0008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>UV-Sheet_0009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>UV-Sheet_0010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>UV-Sheet_0011</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>UV-Sheet_0012</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>UV-Sheet_0013</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>UV-Sheet_0014</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>UV-Sheet_0015</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>UV-Sheet_0016</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>UV-Sheet_0017</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>UV-Sheet_0018</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>UV-Sheet_0019</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>UV-Sheet_0020</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>UV-Sheet_0021</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>UV-Sheet_0022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>UV-Sheet_0023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>UV-Sheet_0024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/UV-Sheets_protocol.xlsx
+++ b/UV-Sheets_protocol.xlsx
@@ -530,7 +530,7 @@
       <c r="J2" t="n">
         <v>10</v>
       </c>
-      <c r="K2" t="b">
+      <c r="K2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -668,7 +668,7 @@
       <c r="J6" t="n">
         <v>5</v>
       </c>
-      <c r="K6" t="b">
+      <c r="K6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -713,7 +713,7 @@
       <c r="J7" t="n">
         <v>6</v>
       </c>
-      <c r="K7" t="b">
+      <c r="K7" t="n">
         <v>1</v>
       </c>
     </row>
